--- a/Assets/Data/Dungeon0041.xlsx
+++ b/Assets/Data/Dungeon0041.xlsx
@@ -138,38 +138,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -177,6 +147,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -192,22 +170,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,7 +200,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -237,6 +208,59 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -250,33 +274,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,7 +291,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,55 +303,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -363,13 +321,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -387,7 +345,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,25 +369,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,7 +405,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -441,19 +429,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -465,13 +453,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,6 +482,75 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -503,45 +572,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -549,36 +579,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,7 +590,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -599,136 +599,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -852,169 +852,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E25" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>

--- a/Assets/Data/Dungeon0041.xlsx
+++ b/Assets/Data/Dungeon0041.xlsx
@@ -138,6 +138,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -160,25 +183,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -199,6 +206,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -206,22 +221,32 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -237,46 +262,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,13 +291,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -309,31 +309,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,25 +333,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,49 +369,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -435,25 +387,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -471,7 +429,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,75 +482,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -572,6 +503,45 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -579,6 +549,36 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,7 +590,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -599,136 +599,136 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0041.xlsx
+++ b/Assets/Data/Dungeon0041.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -73,9 +73,6 @@
     <t>Ev</t>
   </si>
   <si>
-    <t>Dm</t>
-  </si>
-  <si>
     <t>Mg</t>
   </si>
   <si>
@@ -118,8 +115,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -138,82 +135,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -221,17 +142,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -253,6 +165,82 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -261,8 +249,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,13 +274,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -291,7 +288,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,7 +318,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -315,7 +336,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,43 +378,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,43 +450,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,49 +462,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,11 +482,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -497,8 +500,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,15 +517,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -553,6 +547,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -568,17 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -590,145 +587,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2372,12 +2369,8 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
-      <c r="H14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
       <c r="J14" s="2" t="s">
         <v>9</v>
       </c>
@@ -2432,17 +2425,15 @@
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="E15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="H15" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -2667,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>9</v>
@@ -4701,19 +4692,19 @@
         <v>9</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>9</v>
@@ -4772,19 +4763,19 @@
         <v>16</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -4841,19 +4832,19 @@
         <v>9</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>9</v>
@@ -5018,7 +5009,7 @@
         <v>9</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Q18" s="2" t="s">
         <v>9</v>
@@ -6073,7 +6064,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="24.6363636363636" customWidth="1"/>
@@ -6084,34 +6075,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" t="s">
         <v>21</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>27</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>28</v>
-      </c>
-      <c r="K1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -6185,7 +6176,7 @@
         <v>41</v>
       </c>
       <c r="B4">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>13</v>
@@ -6201,7 +6192,7 @@
         <v>強制戦闘</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>3050</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6221,20 +6212,20 @@
         <v>14</v>
       </c>
       <c r="C5">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>3010</v>
+        <v>5010</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F5,[1]Define!D:D))</f>
-        <v>アーティファクト取得</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H5">
-        <v>2130</v>
+        <v>-1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6251,23 +6242,23 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>3020</v>
+        <v>3010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>アイテム取得</v>
+        <v>アーティファクト取得</v>
       </c>
       <c r="H6">
-        <v>3010</v>
+        <v>2130</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6284,10 +6275,10 @@
         <v>41</v>
       </c>
       <c r="B7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>3010</v>
@@ -6300,7 +6291,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H7">
-        <v>1100</v>
+        <v>3010</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6317,10 +6308,10 @@
         <v>41</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>3010</v>
@@ -6333,7 +6324,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H8">
-        <v>4020</v>
+        <v>1100</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -6350,10 +6341,10 @@
         <v>41</v>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>3010</v>
@@ -6366,7 +6357,7 @@
         <v>アイテム取得</v>
       </c>
       <c r="H9">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6383,23 +6374,23 @@
         <v>41</v>
       </c>
       <c r="B10">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D10">
         <v>3010</v>
       </c>
       <c r="F10">
-        <v>1010</v>
+        <v>3020</v>
       </c>
       <c r="G10" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H10">
-        <v>1040</v>
+        <v>3010</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -6425,14 +6416,14 @@
         <v>3010</v>
       </c>
       <c r="F11">
-        <v>9010</v>
+        <v>1010</v>
       </c>
       <c r="G11" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>Adv再生</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -6452,20 +6443,20 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12">
         <v>3010</v>
       </c>
       <c r="F12">
-        <v>1010</v>
+        <v>9010</v>
       </c>
       <c r="G12" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -6491,14 +6482,14 @@
         <v>3010</v>
       </c>
       <c r="F13">
-        <v>6010</v>
+        <v>1010</v>
       </c>
       <c r="G13" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
+        <v>Adv再生</v>
       </c>
       <c r="H13">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -6518,13 +6509,17 @@
         <v>4</v>
       </c>
       <c r="C14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14">
         <v>3010</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>6010</v>
+      </c>
+      <c r="G14" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H14">
         <v>43</v>
@@ -6547,20 +6542,16 @@
         <v>4</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15">
         <v>3010</v>
       </c>
       <c r="F15">
-        <v>5010</v>
-      </c>
-      <c r="G15" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
-        <v>強制戦闘</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>3020</v>
+        <v>43</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -6586,14 +6577,14 @@
         <v>3010</v>
       </c>
       <c r="F16">
-        <v>9010</v>
+        <v>5010</v>
       </c>
       <c r="G16" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F16,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>3020</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -6613,20 +6604,20 @@
         <v>4</v>
       </c>
       <c r="C17">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>3010</v>
       </c>
       <c r="F17">
-        <v>7010</v>
+        <v>9010</v>
       </c>
       <c r="G17" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F17,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H17">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -6635,7 +6626,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -6643,7 +6634,7 @@
         <v>41</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C18">
         <v>13</v>
@@ -6652,14 +6643,14 @@
         <v>3010</v>
       </c>
       <c r="F18">
-        <v>7010</v>
+        <v>8010</v>
       </c>
       <c r="G18" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F18,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>指定リージョンを開示する</v>
       </c>
       <c r="H18">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -6668,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -6676,7 +6667,7 @@
         <v>41</v>
       </c>
       <c r="B19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19">
         <v>13</v>
@@ -6685,14 +6676,14 @@
         <v>3010</v>
       </c>
       <c r="F19">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="G19" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F19,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>Adv再生</v>
       </c>
       <c r="H19">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -6701,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -6712,20 +6703,20 @@
         <v>7</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D20">
         <v>3010</v>
       </c>
       <c r="F20">
-        <v>7010</v>
+        <v>7020</v>
       </c>
       <c r="G20" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F20,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>怨嗟床</v>
       </c>
       <c r="H20">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -6734,7 +6725,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -6758,7 +6749,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H21">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -6784,11 +6775,11 @@
         <v>3010</v>
       </c>
       <c r="F22">
-        <v>7020</v>
+        <v>9010</v>
       </c>
       <c r="G22" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F22,[1]Define!D:D))</f>
-        <v>怨嗟床</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -6808,7 +6799,7 @@
         <v>41</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>13</v>
@@ -6824,7 +6815,7 @@
         <v>Adv再生</v>
       </c>
       <c r="H23">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -6841,7 +6832,7 @@
         <v>41</v>
       </c>
       <c r="B24">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C24">
         <v>13</v>
@@ -6850,11 +6841,11 @@
         <v>3010</v>
       </c>
       <c r="F24">
-        <v>9010</v>
+        <v>7021</v>
       </c>
       <c r="G24" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F24,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>怨嗟床解除</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -6883,17 +6874,17 @@
         <v>3010</v>
       </c>
       <c r="F25">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="G25" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F25,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H25">
-        <v>130</v>
+        <v>3</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -6916,11 +6907,11 @@
         <v>3010</v>
       </c>
       <c r="F26">
-        <v>7021</v>
+        <v>9010</v>
       </c>
       <c r="G26" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F26,[1]Define!D:D))</f>
-        <v>怨嗟床解除</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -6932,105 +6923,6 @@
         <v>0</v>
       </c>
       <c r="K26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27">
-        <v>41</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-      <c r="C27">
-        <v>13</v>
-      </c>
-      <c r="D27">
-        <v>3010</v>
-      </c>
-      <c r="F27">
-        <v>1020</v>
-      </c>
-      <c r="G27" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F27,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
-      </c>
-      <c r="H27">
-        <v>3</v>
-      </c>
-      <c r="I27">
-        <v>2</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28">
-        <v>41</v>
-      </c>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28">
-        <v>13</v>
-      </c>
-      <c r="D28">
-        <v>3010</v>
-      </c>
-      <c r="F28">
-        <v>9010</v>
-      </c>
-      <c r="G28" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F28,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29">
-        <v>41</v>
-      </c>
-      <c r="B29">
-        <v>7</v>
-      </c>
-      <c r="C29">
-        <v>13</v>
-      </c>
-      <c r="D29">
-        <v>3010</v>
-      </c>
-      <c r="F29">
-        <v>8010</v>
-      </c>
-      <c r="G29" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F29,[1]Define!D:D))</f>
-        <v>指定リージョンを開示する</v>
-      </c>
-      <c r="H29">
-        <v>1</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Dungeon0041.xlsx
+++ b/Assets/Data/Dungeon0041.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -115,9 +115,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -132,6 +132,84 @@
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -151,7 +229,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -166,76 +244,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -249,9 +258,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -259,21 +274,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,13 +288,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,7 +312,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,25 +354,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -348,73 +414,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -426,31 +438,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -468,7 +468,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,6 +479,80 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -500,80 +574,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
@@ -587,145 +587,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Dungeon0041.xlsx
+++ b/Assets/Data/Dungeon0041.xlsx
@@ -55,10 +55,10 @@
     <t>Tr</t>
   </si>
   <si>
-    <t>Tr:D1</t>
+    <t>Tr:D3</t>
   </si>
   <si>
-    <t>Tr:D3</t>
+    <t>Tr:D1</t>
   </si>
   <si>
     <t>Dr</t>
@@ -135,17 +135,53 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -159,31 +195,23 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -207,21 +235,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -236,37 +265,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -294,7 +294,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -306,7 +360,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -318,79 +450,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -402,73 +468,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,15 +479,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -506,13 +497,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -528,6 +523,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -556,17 +560,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -574,8 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -587,7 +587,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -596,136 +596,136 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -805,19 +805,17 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
+      <sheetName val="StageEvents"/>
+      <sheetName val="Tutorials"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1032,6 +1030,8 @@
           </cell>
         </row>
       </sheetData>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3970,11 +3970,11 @@
         <v>9</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>9</v>
